--- a/Daily_Report/Top 7 broker List with its Turnover 2024-09-12.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-09-12.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="283">
   <si>
     <t>Date: 2024-09-12</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sumeru Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Siprabi Securities Pvt. Limited</t>
-  </si>
-  <si>
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Bhrikuti Stock Broking Co. Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Premier Securites Company Limited</t>
-  </si>
-  <si>
-    <t>Sundhara Securities Limited</t>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>52</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>45</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>1,154,285,272.4</t>
-  </si>
-  <si>
-    <t>984,998,644.2</t>
-  </si>
-  <si>
-    <t>644,135,301.1</t>
-  </si>
-  <si>
-    <t>554,732,357.5</t>
-  </si>
-  <si>
-    <t>517,602,021.7</t>
-  </si>
-  <si>
-    <t>509,278,109.8</t>
-  </si>
-  <si>
-    <t>492,385,281.8</t>
-  </si>
-  <si>
-    <t>987,052,835.5</t>
-  </si>
-  <si>
-    <t>349,773,045.1</t>
-  </si>
-  <si>
-    <t>419,046,903.8</t>
-  </si>
-  <si>
-    <t>529,023,083.2</t>
-  </si>
-  <si>
-    <t>189,527,454.4</t>
-  </si>
-  <si>
-    <t>421,835,899.8</t>
-  </si>
-  <si>
-    <t>183,412,668.8</t>
-  </si>
-  <si>
-    <t>167,232,436.9</t>
-  </si>
-  <si>
-    <t>635,225,599.1</t>
-  </si>
-  <si>
-    <t>225,088,397.3</t>
-  </si>
-  <si>
-    <t>25,709,274.3</t>
-  </si>
-  <si>
-    <t>328,074,567.3</t>
-  </si>
-  <si>
-    <t>87,442,210.0</t>
-  </si>
-  <si>
-    <t>308,972,613.0</t>
+    <t>57</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>833,318,043.84</t>
+  </si>
+  <si>
+    <t>769,156,437.32</t>
+  </si>
+  <si>
+    <t>608,386,895.6</t>
+  </si>
+  <si>
+    <t>548,716,016.5</t>
+  </si>
+  <si>
+    <t>530,624,454.6</t>
+  </si>
+  <si>
+    <t>526,059,800.6</t>
+  </si>
+  <si>
+    <t>525,845,237.79</t>
+  </si>
+  <si>
+    <t>386,476,425.65</t>
+  </si>
+  <si>
+    <t>363,220,893.12</t>
+  </si>
+  <si>
+    <t>315,698,788.1</t>
+  </si>
+  <si>
+    <t>329,258,028.89</t>
+  </si>
+  <si>
+    <t>307,354,336.89</t>
+  </si>
+  <si>
+    <t>239,883,466.7</t>
+  </si>
+  <si>
+    <t>289,355,761.2</t>
+  </si>
+  <si>
+    <t>446,841,618.2</t>
+  </si>
+  <si>
+    <t>405,935,544.2</t>
+  </si>
+  <si>
+    <t>292,688,107.5</t>
+  </si>
+  <si>
+    <t>219,457,987.6</t>
+  </si>
+  <si>
+    <t>223,270,117.7</t>
+  </si>
+  <si>
+    <t>286,176,333.89</t>
+  </si>
+  <si>
+    <t>236,489,476.6</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,376 +179,349 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>HPPL</t>
+  </si>
+  <si>
+    <t>34,804,979.6</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>28,365,083.8</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>23,537,001.3</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>17,243,746.0</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>10,522,070.19</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>22,330,741.0</t>
+  </si>
+  <si>
+    <t>KRBL</t>
+  </si>
+  <si>
+    <t>21,196,040.0</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>19,610,372.0</t>
+  </si>
+  <si>
+    <t>18,390,913.2</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>14,477,981.9</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>56,181,389.4</t>
+  </si>
+  <si>
+    <t>15,853,824.3</t>
+  </si>
+  <si>
+    <t>TPC</t>
+  </si>
+  <si>
+    <t>15,616,829.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>15,111,708.7</t>
+  </si>
+  <si>
+    <t>11,580,650.0</t>
+  </si>
+  <si>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>47,841,149.0</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>47,512,895.9</t>
+  </si>
+  <si>
     <t>GFCL</t>
   </si>
   <si>
-    <t>406,614,850.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>324,673,755.39</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>116,675,637.0</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>95,237,431.0</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>16,833,650.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>238,526,988.5</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>70,612,680.0</t>
+    <t>31,435,004.1</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>25,725,898.5</t>
+  </si>
+  <si>
+    <t>NWCL</t>
+  </si>
+  <si>
+    <t>15,919,621.0</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>100,071,981.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>33,457,448.0</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>19,191,200.0</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>7,286,513.3</t>
+  </si>
+  <si>
+    <t>7,086,639.7</t>
+  </si>
+  <si>
+    <t>GLH</t>
+  </si>
+  <si>
+    <t>46,076,243.8</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>11,586,518.4</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>11,347,152.6</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>7,346,690.9</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>6,825,599.8</t>
+  </si>
+  <si>
+    <t>32,791,406.3</t>
+  </si>
+  <si>
+    <t>SINDU</t>
+  </si>
+  <si>
+    <t>25,586,135.0</t>
+  </si>
+  <si>
+    <t>MANDU</t>
+  </si>
+  <si>
+    <t>13,146,303.1</t>
+  </si>
+  <si>
+    <t>NICL</t>
+  </si>
+  <si>
+    <t>10,495,748.0</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>9,172,151.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>52,853,970.0</t>
+  </si>
+  <si>
+    <t>34,383,160.2</t>
+  </si>
+  <si>
+    <t>31,474,925.8</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>28,410,839.0</t>
+  </si>
+  <si>
+    <t>ANLB</t>
+  </si>
+  <si>
+    <t>23,256,780.0</t>
+  </si>
+  <si>
+    <t>67,636,083.3</t>
+  </si>
+  <si>
+    <t>35,408,610.1</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>35,157,124.0</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>15,073,854.8</t>
+  </si>
+  <si>
+    <t>8,542,579.0</t>
+  </si>
+  <si>
+    <t>25,708,220.4</t>
+  </si>
+  <si>
+    <t>23,749,264.2</t>
+  </si>
+  <si>
+    <t>12,987,296.0</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>12,572,251.0</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>8,640,622.0</t>
+  </si>
+  <si>
+    <t>MSLB</t>
+  </si>
+  <si>
+    <t>27,066,236.6</t>
   </si>
   <si>
     <t>ALICL</t>
   </si>
   <si>
-    <t>7,111,700.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>5,882,415.0</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>5,476,600.0</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>204,110,719.0</t>
-  </si>
-  <si>
-    <t>BHL</t>
-  </si>
-  <si>
-    <t>44,841,615.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>39,733,702.5</t>
-  </si>
-  <si>
-    <t>SLBBL</t>
-  </si>
-  <si>
-    <t>25,721,720.0</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>20,526,083.8</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>285,678,700.0</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>174,389,325.0</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>47,969,500.0</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>5,081,580.0</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>3,884,643.0</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>60,434,500.0</t>
-  </si>
-  <si>
-    <t>HLBSL</t>
-  </si>
-  <si>
-    <t>43,636,012.2</t>
-  </si>
-  <si>
-    <t>RBCL</t>
-  </si>
-  <si>
-    <t>36,732,620.0</t>
-  </si>
-  <si>
-    <t>GUFL</t>
-  </si>
-  <si>
-    <t>31,691,364.0</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>9,598,450.0</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>195,004,784.0</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>84,835,190.0</t>
-  </si>
-  <si>
-    <t>68,074,992.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>45,507,000.0</t>
-  </si>
-  <si>
-    <t>MSLB</t>
-  </si>
-  <si>
-    <t>9,875,019.0</t>
-  </si>
-  <si>
-    <t>MLBS</t>
-  </si>
-  <si>
-    <t>78,051,400.0</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>28,228,200.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>22,233,787.2</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>17,989,317.5</t>
-  </si>
-  <si>
-    <t>UNHPL</t>
-  </si>
-  <si>
-    <t>5,397,800.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>30,277,029.0</t>
-  </si>
-  <si>
-    <t>28,427,100.0</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>24,784,839.7</t>
-  </si>
-  <si>
-    <t>21,603,680.0</t>
-  </si>
-  <si>
-    <t>13,297,500.0</t>
-  </si>
-  <si>
-    <t>467,462,093.6</t>
-  </si>
-  <si>
-    <t>USLB</t>
-  </si>
-  <si>
-    <t>47,280,000.0</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>44,772,702.3</t>
-  </si>
-  <si>
-    <t>SMHL</t>
-  </si>
-  <si>
-    <t>24,351,500.0</t>
-  </si>
-  <si>
-    <t>CZBIL</t>
-  </si>
-  <si>
-    <t>14,206,458.0</t>
-  </si>
-  <si>
-    <t>62,243,288.0</t>
-  </si>
-  <si>
-    <t>34,522,686.5</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>34,475,000.0</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
-    <t>19,862,413.0</t>
-  </si>
-  <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>12,844,400.0</t>
-  </si>
-  <si>
-    <t>9,576,630.0</t>
-  </si>
-  <si>
-    <t>HBL</t>
-  </si>
-  <si>
-    <t>8,063,241.1</t>
-  </si>
-  <si>
-    <t>UMHL</t>
-  </si>
-  <si>
-    <t>2,557,848.0</t>
-  </si>
-  <si>
-    <t>1,154,966.0</t>
-  </si>
-  <si>
-    <t>428,930.0</t>
+    <t>25,696,474.0</t>
+  </si>
+  <si>
+    <t>23,850,249.0</t>
+  </si>
+  <si>
+    <t>16,342,198.5</t>
+  </si>
+  <si>
+    <t>RAWA</t>
+  </si>
+  <si>
+    <t>5,720,880.0</t>
+  </si>
+  <si>
+    <t>36,379,936.2</t>
+  </si>
+  <si>
+    <t>10,803,756.5</t>
+  </si>
+  <si>
+    <t>8,932,440.0</t>
   </si>
   <si>
     <t>CHDC</t>
   </si>
   <si>
-    <t>131,548,713.0</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>71,528,813.5</t>
-  </si>
-  <si>
-    <t>41,370,000.0</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>25,511,500.0</t>
-  </si>
-  <si>
-    <t>13,784,484.0</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
-    <t>47,871,000.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>13,034,620.0</t>
-  </si>
-  <si>
-    <t>6,225,200.0</t>
-  </si>
-  <si>
-    <t>4,150,987.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>2,874,300.0</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>104,799,600.0</t>
-  </si>
-  <si>
-    <t>SMPDA</t>
-  </si>
-  <si>
-    <t>86,522,400.0</t>
-  </si>
-  <si>
-    <t>47,469,550.0</t>
-  </si>
-  <si>
-    <t>25,519,279.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>13,533,900.0</t>
+    <t>7,973,452.0</t>
+  </si>
+  <si>
+    <t>4,733,371.4</t>
+  </si>
+  <si>
+    <t>ENL</t>
+  </si>
+  <si>
+    <t>103,272,299.0</t>
+  </si>
+  <si>
+    <t>21,092,653.0</t>
+  </si>
+  <si>
+    <t>5,316,906.8</t>
+  </si>
+  <si>
+    <t>4,916,197.3</t>
+  </si>
+  <si>
+    <t>4,323,319.0</t>
+  </si>
+  <si>
+    <t>24,822,786.2</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>21,135,970.0</t>
+  </si>
+  <si>
+    <t>14,092,618.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>8,289,241.0</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>8,266,850.5</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -566,112 +539,112 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>498,235,309.0</t>
-  </si>
-  <si>
-    <t>469,581,784.6</t>
-  </si>
-  <si>
-    <t>423,692,338.4</t>
-  </si>
-  <si>
-    <t>334,253,830.0</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>286,360,716.0</t>
+    <t>267,900,273.2</t>
+  </si>
+  <si>
+    <t>224,697,262.4</t>
+  </si>
+  <si>
+    <t>223,346,523.9</t>
+  </si>
+  <si>
+    <t>194,431,677.4</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>164,945,076.9</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,681,806,951.4</t>
+    <t>1,949,141,261.5</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>1,791,958,007.03</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,662,504,453.0</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>1,393,740,353.5</t>
+    <t>926,398,032.0</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>780,962,236.9</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>843,396,332.6</t>
+    <t>570,098,926.79</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>489,254,647.8</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>725,409,283.9</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>652,563,467.79</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>630,255,958.7</t>
+    <t>411,700,878.2</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>352,599,299.5</t>
+    <t>243,098,400.1</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>257,449,769.6</t>
+    <t>176,288,206.4</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>173,825,543.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>242,727,097.5</t>
+    <t>115,001,779.2</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>63,352,493.8</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>46,339,123.5</t>
+    <t>79,931,136.7</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>5,652,930.0</t>
+    <t>39,831,420.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>647,022.19</t>
+    <t>10,696,890.24</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>45,000.0</t>
+    <t>638,090.5</t>
   </si>
   <si>
     <t>Total</t>
@@ -683,208 +656,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>731,631,105.4</t>
-  </si>
-  <si>
-    <t>116,857,820.0</t>
-  </si>
-  <si>
-    <t>108,774,932.6</t>
-  </si>
-  <si>
-    <t>23,110,514.5</t>
-  </si>
-  <si>
-    <t>4,377,600.0</t>
-  </si>
-  <si>
-    <t>241,592,270.0</t>
-  </si>
-  <si>
-    <t>86,468,483.4</t>
-  </si>
-  <si>
-    <t>6,637,733.9</t>
-  </si>
-  <si>
-    <t>5,676,343.8</t>
-  </si>
-  <si>
-    <t>210,048,939.0</t>
-  </si>
-  <si>
-    <t>67,314,394.59</t>
-  </si>
-  <si>
-    <t>61,043,183.3</t>
-  </si>
-  <si>
-    <t>28,086,147.5</t>
-  </si>
-  <si>
-    <t>24,517,072.9</t>
-  </si>
-  <si>
-    <t>288,979,279.0</t>
-  </si>
-  <si>
-    <t>175,774,548.4</t>
-  </si>
-  <si>
-    <t>55,368,616.4</t>
-  </si>
-  <si>
-    <t>5,112,980.0</t>
-  </si>
-  <si>
-    <t>3,376,788.4</t>
-  </si>
-  <si>
-    <t>104,981,862.4</t>
-  </si>
-  <si>
-    <t>37,083,902.0</t>
-  </si>
-  <si>
-    <t>32,001,657.0</t>
-  </si>
-  <si>
-    <t>14,163,000.0</t>
-  </si>
-  <si>
-    <t>494,650.0</t>
-  </si>
-  <si>
-    <t>195,110,884.0</t>
-  </si>
-  <si>
-    <t>77,664,454.3</t>
-  </si>
-  <si>
-    <t>47,792,774.0</t>
-  </si>
-  <si>
-    <t>10,438,045.5</t>
-  </si>
-  <si>
-    <t>78,954,759.5</t>
-  </si>
-  <si>
-    <t>28,250,550.0</t>
-  </si>
-  <si>
-    <t>23,165,057.2</t>
-  </si>
-  <si>
-    <t>18,415,662.5</t>
-  </si>
-  <si>
-    <t>14,468,936.2</t>
-  </si>
-  <si>
-    <t>59,316,471.5</t>
-  </si>
-  <si>
-    <t>46,538,915.2</t>
-  </si>
-  <si>
-    <t>29,533,137.0</t>
-  </si>
-  <si>
-    <t>13,678,805.0</t>
-  </si>
-  <si>
-    <t>11,746,746.7</t>
-  </si>
-  <si>
-    <t>482,203,686.4</t>
-  </si>
-  <si>
-    <t>58,198,720.5</t>
-  </si>
-  <si>
-    <t>48,437,166.7</t>
-  </si>
-  <si>
-    <t>26,814,524.5</t>
-  </si>
-  <si>
-    <t>13,103,054.0</t>
-  </si>
-  <si>
-    <t>72,193,647.0</t>
-  </si>
-  <si>
-    <t>64,710,405.4</t>
-  </si>
-  <si>
-    <t>34,500,950.0</t>
-  </si>
-  <si>
-    <t>26,426,882.4</t>
-  </si>
-  <si>
-    <t>11,215,821.0</t>
-  </si>
-  <si>
-    <t>12,512,318.0</t>
-  </si>
-  <si>
-    <t>8,096,947.1</t>
-  </si>
-  <si>
-    <t>2,574,667.79</t>
-  </si>
-  <si>
-    <t>1,514,864.2</t>
-  </si>
-  <si>
-    <t>422,947.6</t>
-  </si>
-  <si>
-    <t>135,068,674.6</t>
-  </si>
-  <si>
-    <t>81,671,214.59</t>
-  </si>
-  <si>
-    <t>41,684,032.0</t>
-  </si>
-  <si>
-    <t>38,373,866.4</t>
-  </si>
-  <si>
-    <t>14,697,681.1</t>
-  </si>
-  <si>
-    <t>48,390,100.0</t>
-  </si>
-  <si>
-    <t>15,829,820.2</t>
-  </si>
-  <si>
-    <t>10,471,366.0</t>
-  </si>
-  <si>
-    <t>4,784,043.0</t>
-  </si>
-  <si>
-    <t>2,869,687.0</t>
-  </si>
-  <si>
-    <t>202,766,393.4</t>
-  </si>
-  <si>
-    <t>61,905,570.0</t>
-  </si>
-  <si>
-    <t>28,358,378.0</t>
-  </si>
-  <si>
-    <t>10,804,370.4</t>
-  </si>
-  <si>
-    <t>2,564,969.0</t>
+    <t>100,259,005.5</t>
+  </si>
+  <si>
+    <t>79,755,072.0</t>
+  </si>
+  <si>
+    <t>61,495,621.2</t>
+  </si>
+  <si>
+    <t>46,733,632.4</t>
+  </si>
+  <si>
+    <t>28,827,045.9</t>
+  </si>
+  <si>
+    <t>99,506,134.0</t>
+  </si>
+  <si>
+    <t>74,547,518.3</t>
+  </si>
+  <si>
+    <t>44,510,877.6</t>
+  </si>
+  <si>
+    <t>38,468,409.9</t>
+  </si>
+  <si>
+    <t>24,841,906.3</t>
+  </si>
+  <si>
+    <t>67,989,596.3</t>
+  </si>
+  <si>
+    <t>65,609,648.8</t>
+  </si>
+  <si>
+    <t>55,530,792.2</t>
+  </si>
+  <si>
+    <t>45,659,885.5</t>
+  </si>
+  <si>
+    <t>20,760,476.89</t>
+  </si>
+  <si>
+    <t>74,726,622.7</t>
+  </si>
+  <si>
+    <t>55,436,838.4</t>
+  </si>
+  <si>
+    <t>53,412,860.6</t>
+  </si>
+  <si>
+    <t>50,371,256.0</t>
+  </si>
+  <si>
+    <t>46,110,317.4</t>
+  </si>
+  <si>
+    <t>163,192,248.69</t>
+  </si>
+  <si>
+    <t>58,068,491.7</t>
+  </si>
+  <si>
+    <t>20,999,083.0</t>
+  </si>
+  <si>
+    <t>17,474,157.39</t>
+  </si>
+  <si>
+    <t>13,850,229.6</t>
+  </si>
+  <si>
+    <t>92,821,377.5</t>
+  </si>
+  <si>
+    <t>54,733,308.7</t>
+  </si>
+  <si>
+    <t>24,773,698.2</t>
+  </si>
+  <si>
+    <t>21,312,674.2</t>
+  </si>
+  <si>
+    <t>12,752,228.1</t>
+  </si>
+  <si>
+    <t>85,751,657.2</t>
+  </si>
+  <si>
+    <t>53,756,913.4</t>
+  </si>
+  <si>
+    <t>39,413,905.5</t>
+  </si>
+  <si>
+    <t>34,171,917.2</t>
+  </si>
+  <si>
+    <t>18,695,806.39</t>
+  </si>
+  <si>
+    <t>171,390,215.69</t>
+  </si>
+  <si>
+    <t>131,994,438.2</t>
+  </si>
+  <si>
+    <t>41,172,422.7</t>
+  </si>
+  <si>
+    <t>28,009,897.5</t>
+  </si>
+  <si>
+    <t>22,786,043.0</t>
+  </si>
+  <si>
+    <t>127,017,129.7</t>
+  </si>
+  <si>
+    <t>109,840,241.8</t>
+  </si>
+  <si>
+    <t>52,272,510.6</t>
+  </si>
+  <si>
+    <t>35,065,086.1</t>
+  </si>
+  <si>
+    <t>19,805,501.6</t>
+  </si>
+  <si>
+    <t>74,331,491.09</t>
+  </si>
+  <si>
+    <t>50,163,065.6</t>
+  </si>
+  <si>
+    <t>37,247,075.1</t>
+  </si>
+  <si>
+    <t>31,620,689.1</t>
+  </si>
+  <si>
+    <t>25,181,789.5</t>
+  </si>
+  <si>
+    <t>46,366,750.4</t>
+  </si>
+  <si>
+    <t>38,589,684.6</t>
+  </si>
+  <si>
+    <t>35,612,548.0</t>
+  </si>
+  <si>
+    <t>33,829,926.6</t>
+  </si>
+  <si>
+    <t>27,836,387.7</t>
+  </si>
+  <si>
+    <t>76,442,904.5</t>
+  </si>
+  <si>
+    <t>56,675,937.9</t>
+  </si>
+  <si>
+    <t>21,419,926.39</t>
+  </si>
+  <si>
+    <t>18,115,448.2</t>
+  </si>
+  <si>
+    <t>15,976,150.2</t>
+  </si>
+  <si>
+    <t>114,467,662.8</t>
+  </si>
+  <si>
+    <t>59,095,205.2</t>
+  </si>
+  <si>
+    <t>40,154,242.6</t>
+  </si>
+  <si>
+    <t>15,718,334.7</t>
+  </si>
+  <si>
+    <t>15,186,808.5</t>
+  </si>
+  <si>
+    <t>71,075,546.5</t>
+  </si>
+  <si>
+    <t>41,318,624.1</t>
+  </si>
+  <si>
+    <t>35,966,541.4</t>
+  </si>
+  <si>
+    <t>19,944,822.8</t>
+  </si>
+  <si>
+    <t>17,064,337.3</t>
   </si>
 </sst>
 </file>
@@ -1693,7 +1672,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.3522654752014316</v>
+        <v>0.04176674183028373</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1702,52 +1681,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2421597125077545</v>
+        <v>0.0290327687795318</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.316875536322007</v>
+        <v>0.09234483813888381</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.5149847419888428</v>
+        <v>0.08718744771686467</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1167586243220425</v>
+        <v>0.1885928553282324</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S9" s="16">
-        <v>0.3829043115098367</v>
+        <v>0.08758746391084725</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1585169234032941</v>
+        <v>0.06235942429980109</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1759,7 +1738,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.2812768759709941</v>
+        <v>0.03403872508142379</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1768,52 +1747,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.07168809867484688</v>
+        <v>0.02755751492356242</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.06961521115738148</v>
+        <v>0.02605878662847385</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.3143665997525663</v>
+        <v>0.08658922734397713</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P10" s="18">
-        <v>0.0843041765112951</v>
+        <v>0.06305297034457484</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1665792979661267</v>
+        <v>0.02202509750181432</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="V10" s="18">
-        <v>0.05732949591183333</v>
+        <v>0.04865715834386131</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1825,7 +1804,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.1010804172848944</v>
+        <v>0.02824491978027628</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1834,52 +1813,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.007220009937958857</v>
+        <v>0.02549594731122467</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06168533603444203</v>
+        <v>0.0256692396120703</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.086473232273998</v>
+        <v>0.05728829331519977</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P11" s="18">
-        <v>0.07096691755444895</v>
+        <v>0.03616719854057025</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="S11" s="16">
-        <v>0.1336695818847072</v>
+        <v>0.0215700811714903</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04515526361535528</v>
+        <v>0.02500032738719993</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1891,61 +1870,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.08250770695703455</v>
+        <v>0.02069287486003835</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.00597200314400189</v>
+        <v>0.02391049766687273</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03993216946202857</v>
+        <v>0.02483897797485696</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.009160417508185468</v>
+        <v>0.04688381189252201</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P12" s="18">
-        <v>0.06122728017157588</v>
+        <v>0.01373195908487253</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="S12" s="16">
-        <v>0.08935589243737803</v>
+        <v>0.01396550523651626</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03653504311549875</v>
+        <v>0.01995976619263776</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1957,61 +1936,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01458361325619214</v>
+        <v>0.0126267159071549</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.005560007653054188</v>
+        <v>0.01882319538330351</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03186610602608999</v>
+        <v>0.01903500894538334</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.007002733746246269</v>
+        <v>0.02901249557383751</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01854407362721474</v>
+        <v>0.0133552828908764</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01939022865891103</v>
+        <v>0.01297495036156542</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01096255351148475</v>
+        <v>0.01744268149764729</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2022,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2031,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2040,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2049,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2058,7 +2037,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2067,7 +2046,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2076,7 +2055,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2085,67 +2064,67 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D16" s="10">
-        <v>0.02623010942264535</v>
+        <v>0.06342592769959736</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4745814589213624</v>
+        <v>0.08793540561874108</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J16" s="14">
-        <v>0.0966307666940566</v>
+        <v>0.04225636775862205</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="M16" s="16">
-        <v>0.01726351432456327</v>
+        <v>0.04932649273232942</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="O16" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.06856060983360492</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="P16" s="18">
-        <v>0.2541503075431283</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="R16" s="15" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="S16" s="16">
-        <v>0.09399775697957949</v>
+        <v>0.1963128505204395</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2128406430364589</v>
+        <v>0.0472054977693667</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2154,497 +2133,497 @@
         <v>54</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D17" s="10">
-        <v>0.02462744754673524</v>
+        <v>0.04126054926297634</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G17" s="12">
-        <v>0.04800006606953256</v>
+        <v>0.04603564162236687</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J17" s="14">
-        <v>0.05359539593784887</v>
+        <v>0.03903644929198899</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01453537186173604</v>
+        <v>0.04683018761490809</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="O17" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.02036045720535851</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="P17" s="18">
-        <v>0.1381926856952228</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="S17" s="16">
-        <v>0.02559430642938661</v>
+        <v>0.04009554232416671</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1757209307388359</v>
+        <v>0.0401942786216481</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02147202281154219</v>
+        <v>0.03777060395162354</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G18" s="12">
-        <v>0.04545458266733318</v>
+        <v>0.04570867809739623</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05352136413130362</v>
+        <v>0.02134710016590962</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="L18" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.04346556011273274</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="O18" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.004610958718051705</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="O18" s="17" t="s">
+      <c r="P18" s="18">
+        <v>0.01683382648983551</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="R18" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="P18" s="18">
-        <v>0.07992627204995323</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="S18" s="16">
-        <v>0.01222357662779717</v>
+        <v>0.01010703876999493</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="V18" s="18">
-        <v>0.09640732928991461</v>
+        <v>0.02679993463278256</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01871606657085855</v>
+        <v>0.03409363232882792</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02472236905440402</v>
+        <v>0.01959790501464486</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03083577777227959</v>
+        <v>0.02066489447903223</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="L19" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.02978261615951937</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.002082023852376414</v>
-      </c>
-      <c r="N19" s="17" t="s">
+      <c r="O19" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.01502654453800215</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="O19" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.04928786776413783</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>167</v>
-      </c>
       <c r="S19" s="16">
-        <v>0.008150727314060574</v>
+        <v>0.00934532023620282</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05182786720738248</v>
+        <v>0.01576365136381197</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01152011579628987</v>
+        <v>0.02790864805057107</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0144228198522428</v>
+        <v>0.01110642593041959</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01994053109349141</v>
+        <v>0.01420251169525684</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0007732197233510036</v>
+        <v>0.01042593951693043</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02663143384704442</v>
+        <v>0.008920379298327199</v>
       </c>
       <c r="Q20" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.008218303308994564</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="R20" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.005643871088684283</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>177</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.02748640241748184</v>
+        <v>0.01572107134522385</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2058698025358099</v>
+        <v>0.2385941658080154</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2035069858458516</v>
+        <v>0.2193533810480655</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1706076022116476</v>
+        <v>0.1134002804297143</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1032400516047649</v>
+        <v>0.09559750086934229</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D35" s="22">
-        <v>0.08879727004922897</v>
+        <v>0.06978574644877827</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D36" s="22">
-        <v>0.07988022177351392</v>
+        <v>0.05988960721589823</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D37" s="22">
-        <v>0.07714956205679684</v>
+        <v>0.05039625887400381</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D38" s="22">
-        <v>0.0431616411752274</v>
+        <v>0.02975764821503301</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D39" s="22">
-        <v>0.03151439776504765</v>
+        <v>0.0215794198084084</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02971219710491636</v>
+        <v>0.02127796556470623</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D41" s="22">
-        <v>0.00775497174506275</v>
+        <v>0.01407735504688128</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D42" s="22">
-        <v>0.005672366972134463</v>
+        <v>0.009784361585135395</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D43" s="22">
-        <v>0.0006919745348180371</v>
+        <v>0.004875759707911094</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D44" s="22">
-        <v>7.920191579622301E-05</v>
+        <v>0.001309405148803117</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D45" s="22">
-        <v>5.508445012906877E-06</v>
+        <v>7.810858738907234E-05</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3023,331 +3002,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D9" s="10">
-        <v>0.6338390715830465</v>
+        <v>0.1203130140285873</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2452716777049143</v>
+        <v>0.1293704754610296</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3260944379873236</v>
+        <v>0.1117538802885418</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="M9" s="16">
-        <v>0.5209346004302624</v>
+        <v>0.1361845115742125</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2028235169082223</v>
+        <v>0.3075475456988107</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="S9" s="16">
-        <v>0.383112645616405</v>
+        <v>0.1764464370669117</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1603515832385711</v>
+        <v>0.1630739446434139</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1012382491522466</v>
+        <v>0.09570784238815329</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G10" s="12">
-        <v>0.0877853831669264</v>
+        <v>0.09692113942353348</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1045035018031866</v>
+        <v>0.1078419822558716</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="M10" s="16">
-        <v>0.3168637019700081</v>
+        <v>0.1010301079848286</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="P10" s="18">
-        <v>0.07164558955585702</v>
+        <v>0.109434254672212</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1665792979661267</v>
+        <v>0.1040438912792304</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="V10" s="18">
-        <v>0.05737488719550106</v>
+        <v>0.102229533588447</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D11" s="10">
-        <v>0.0942357450111394</v>
+        <v>0.07379609940507831</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="G11" s="12">
-        <v>0.007220009937958857</v>
+        <v>0.05786973291817057</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0947676415122034</v>
+        <v>0.09127545744593123</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M11" s="16">
-        <v>0.09981140571919855</v>
+        <v>0.09734153732325035</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06182676198770341</v>
+        <v>0.03957428425689449</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="S11" s="16">
-        <v>0.1524991017785937</v>
+        <v>0.04709293158637904</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04704660772010915</v>
+        <v>0.07495343242984867</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02002149299882204</v>
+        <v>0.05608138782653339</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G12" s="12">
-        <v>0.006738825417765991</v>
+        <v>0.05001376577440721</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0436028695400436</v>
+        <v>0.07505073799291741</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M12" s="16">
-        <v>0.009217021381342443</v>
+        <v>0.09179840661713216</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="P12" s="18">
-        <v>0.0273627215625692</v>
+        <v>0.03293130810032591</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="S12" s="16">
-        <v>0.09384415524705908</v>
+        <v>0.0405137860290631</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0374009199313967</v>
+        <v>0.06498474217046528</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D13" s="10">
-        <v>0.003792476699367441</v>
+        <v>0.03459308977256343</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G13" s="12">
-        <v>0.005762793515934466</v>
+        <v>0.03229759915493598</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03806199234560163</v>
+        <v>0.03412380682448085</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="M13" s="16">
-        <v>0.006087238925845425</v>
+        <v>0.08403311733839283</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0009556570091735403</v>
+        <v>0.02610175516776871</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02049576704582719</v>
+        <v>0.02424102371147802</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02938539541049295</v>
+        <v>0.03555381898715752</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3358,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3367,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3376,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3385,7 +3364,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3394,7 +3373,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3403,7 +3382,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3412,7 +3391,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3421,331 +3400,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D16" s="10">
-        <v>0.05138805191256462</v>
+        <v>0.2056720323829335</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G16" s="12">
-        <v>0.4895475635823215</v>
+        <v>0.1651382261618592</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1120783892401391</v>
+        <v>0.1221779950186028</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M16" s="16">
-        <v>0.02255559429846311</v>
+        <v>0.08450045015225102</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2609508250303652</v>
+        <v>0.144062158909779</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="S16" s="16">
-        <v>0.09501704288645629</v>
+        <v>0.2175943926326311</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="V16" s="18">
-        <v>0.4118043347249378</v>
+        <v>0.1351643818195666</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04031838256346794</v>
+        <v>0.158396231995859</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G17" s="12">
-        <v>0.05908507675893103</v>
+        <v>0.1428061139067111</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1004608896446026</v>
+        <v>0.08245257411491162</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01459613269449493</v>
+        <v>0.0703272429446207</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1577876653799785</v>
+        <v>0.1068098867450878</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="S17" s="16">
-        <v>0.03108286002360591</v>
+        <v>0.1123355275058058</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1257258742050401</v>
+        <v>0.07857563619453208</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02558564828484248</v>
+        <v>0.04940781374393374</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G18" s="12">
-        <v>0.04917485621448737</v>
+        <v>0.06796083093594722</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05356165069835822</v>
+        <v>0.06122267815000584</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M18" s="16">
-        <v>0.004641279285749975</v>
+        <v>0.06490160106343461</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="P18" s="18">
-        <v>0.08053297756274973</v>
+        <v>0.04036739395312445</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02056119396946442</v>
+        <v>0.0763301863290103</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05759387830670124</v>
+        <v>0.06839757939137127</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D19" s="10">
-        <v>0.0118504544128497</v>
+        <v>0.03361249370119469</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0272229049835681</v>
+        <v>0.04558901726439236</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J19" s="14">
-        <v>0.04102691213301055</v>
+        <v>0.05197463871869761</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M19" s="16">
-        <v>0.002730801943530038</v>
+        <v>0.06165288707223293</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="P19" s="18">
-        <v>0.07413778306731833</v>
+        <v>0.03413986679836674</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="S19" s="16">
-        <v>0.009393773083784722</v>
+        <v>0.02987936862324849</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0219429190907225</v>
+        <v>0.03792907373934575</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01017664088841406</v>
+        <v>0.02734375328623217</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01330261120373631</v>
+        <v>0.02574964030595523</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01741221290130593</v>
+        <v>0.04139107808225447</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="M20" s="16">
-        <v>0.000762435423644816</v>
+        <v>0.05073004407189561</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02839571810737384</v>
+        <v>0.03010820564620091</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="S20" s="16">
-        <v>0.005634813169423211</v>
+        <v>0.0288689774103222</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="V20" s="18">
-        <v>0.00520927228089213</v>
+        <v>0.03245125385444729</v>
       </c>
     </row>
   </sheetData>
